--- a/plantillas/eleccion/Levantada_Distrito.xlsx
+++ b/plantillas/eleccion/Levantada_Distrito.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\eleccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6335C974-D710-4BAC-99F8-9214268A6805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F9B02D-C106-4197-B7F6-8C508625623B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15120" yWindow="2220" windowWidth="21600" windowHeight="11295" xr2:uid="{FACD4310-A9D5-471E-BE84-C61A88BD61FC}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FACD4310-A9D5-471E-BE84-C61A88BD61FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,7 +147,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +500,7 @@
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
     </row>
@@ -512,10 +515,10 @@
     <row r="8" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="E8" s="4"/>
+      <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="E9" s="4"/>
+      <c r="E9" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
